--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
@@ -8288,7 +8288,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6044,7 +6044,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8288,7 +8288,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6044,7 +6044,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8288,7 +8288,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6044,7 +6044,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6044,7 +6044,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6044,7 +6044,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
@@ -6336,7 +6336,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6044,7 +6044,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
@@ -6336,7 +6336,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8288,7 +8288,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
@@ -6336,7 +6336,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6044,7 +6044,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8288,7 +8288,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6044,7 +6044,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8288,7 +8288,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6044,7 +6044,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8288,7 +8288,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6044,7 +6044,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8288,7 +8288,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
@@ -6336,7 +6336,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8288,7 +8288,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6044,7 +6044,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6044,7 +6044,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6044,7 +6044,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8288,7 +8288,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6044,7 +6044,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8288,7 +8288,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
@@ -8288,7 +8288,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
@@ -6336,7 +6336,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8288,7 +8288,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
@@ -6336,7 +6336,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8288,7 +8288,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6044,7 +6044,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8288,7 +8288,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260608_213439.xlsx
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6044,7 +6044,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8288,7 +8288,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
